--- a/public/tableau-synthese-bts-sio.xlsx
+++ b/public/tableau-synthese-bts-sio.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="41">
   <si>
     <t xml:space="preserve">BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -52,27 +52,7 @@
     <t xml:space="preserve">▢ SLAM</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="18"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Adresse URL du portfolio :</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="18"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">https://bts-sisr-showcase.lovable.app/</t>
-    </r>
+    <t xml:space="preserve">Adresse URL du portfolio :https://bts-sisr-showcase.lovable.app/</t>
   </si>
   <si>
     <t xml:space="preserve">Compétences mises en œuvre
@@ -142,16 +122,19 @@
     <t xml:space="preserve">Projet 1 : Interconnexction de 3 site distant</t>
   </si>
   <si>
+    <t xml:space="preserve">X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fichier technique et schéma du projet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Déploiment du spanning tree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projet 2 :Réseaux VPN et mise en place d’un serveur applicatif</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fichier et schéma du projet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Déploiment du spanning tree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Projet 2 : Petite baie transportable contactant un serveur aplicatif via un VPN</t>
   </si>
   <si>
     <t xml:space="preserve">gestion de l’aplicatif sur le serveur</t>
@@ -639,7 +622,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -960,17 +943,19 @@
       <c r="C9" s="20"/>
       <c r="D9" s="21"/>
       <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
+      <c r="F9" s="21" t="s">
+        <v>26</v>
+      </c>
       <c r="G9" s="21"/>
       <c r="H9" s="22"/>
     </row>
     <row r="10" s="16" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B10" s="19"/>
       <c r="C10" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D10" s="21"/>
       <c r="E10" s="21"/>
@@ -988,7 +973,7 @@
       <c r="E11" s="21"/>
       <c r="F11" s="21"/>
       <c r="G11" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H11" s="22"/>
     </row>
@@ -1026,11 +1011,11 @@
     </row>
     <row r="15" s="16" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="18" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B15" s="19"/>
       <c r="C15" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D15" s="21"/>
       <c r="E15" s="21"/>
@@ -1040,12 +1025,12 @@
     </row>
     <row r="16" s="16" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="21"/>
       <c r="D16" s="23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E16" s="21"/>
       <c r="F16" s="21"/>
@@ -1054,7 +1039,7 @@
     </row>
     <row r="17" s="16" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B17" s="19"/>
       <c r="C17" s="21"/>
@@ -1062,7 +1047,7 @@
       <c r="E17" s="21"/>
       <c r="F17" s="21"/>
       <c r="G17" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H17" s="22"/>
     </row>
@@ -1078,7 +1063,7 @@
     </row>
     <row r="19" s="16" customFormat="true" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B19" s="24"/>
       <c r="C19" s="24"/>
@@ -1090,28 +1075,28 @@
     </row>
     <row r="20" s="16" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B20" s="19"/>
       <c r="C20" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D20" s="21"/>
       <c r="E20" s="21"/>
       <c r="F20" s="21"/>
       <c r="G20" s="21"/>
       <c r="H20" s="22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" s="16" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B21" s="19"/>
       <c r="C21" s="21"/>
       <c r="D21" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E21" s="21"/>
       <c r="F21" s="21"/>
@@ -1120,7 +1105,7 @@
     </row>
     <row r="22" s="16" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B22" s="19"/>
       <c r="C22" s="21"/>
@@ -1128,13 +1113,13 @@
       <c r="E22" s="21"/>
       <c r="F22" s="21"/>
       <c r="G22" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H22" s="22"/>
     </row>
     <row r="23" s="16" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B23" s="19"/>
       <c r="C23" s="21"/>
@@ -1143,7 +1128,7 @@
       <c r="F23" s="21"/>
       <c r="G23" s="21"/>
       <c r="H23" s="22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" s="16" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1178,7 +1163,7 @@
     </row>
     <row r="27" s="16" customFormat="true" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B27" s="24"/>
       <c r="C27" s="24"/>
@@ -1190,27 +1175,27 @@
     </row>
     <row r="28" s="16" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B28" s="19"/>
       <c r="C28" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D28" s="21"/>
       <c r="E28" s="21"/>
       <c r="F28" s="23"/>
       <c r="G28" s="21"/>
       <c r="H28" s="22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" s="16" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29" s="19"/>
       <c r="C29" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D29" s="21"/>
       <c r="E29" s="21"/>
@@ -1220,12 +1205,12 @@
     </row>
     <row r="30" s="16" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B30" s="19"/>
       <c r="C30" s="21"/>
       <c r="D30" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E30" s="21"/>
       <c r="F30" s="21"/>
@@ -1234,23 +1219,23 @@
     </row>
     <row r="31" s="16" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B31" s="19"/>
       <c r="C31" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D31" s="21"/>
       <c r="E31" s="21"/>
       <c r="F31" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G31" s="21"/>
       <c r="H31" s="22"/>
     </row>
     <row r="32" s="16" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B32" s="19"/>
       <c r="C32" s="21"/>
@@ -1258,13 +1243,13 @@
       <c r="E32" s="21"/>
       <c r="F32" s="21"/>
       <c r="G32" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H32" s="22"/>
     </row>
     <row r="33" s="16" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B33" s="19"/>
       <c r="C33" s="21"/>
@@ -1273,7 +1258,7 @@
       <c r="F33" s="21"/>
       <c r="G33" s="21"/>
       <c r="H33" s="22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="34" s="16" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1312,7 +1297,7 @@
     <mergeCell ref="A27:H27"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A5" r:id="rId1" display="https://bts-sisr-showcase.lovable.app/"/>
+    <hyperlink ref="A5" r:id="rId1" display="Adresse URL du portfolio :https://bts-sisr-showcase.lovable.app/"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="true"/>
   <pageMargins left="0.196527777777778" right="0.196527777777778" top="0.196527777777778" bottom="0.196527777777778" header="0.511811023622047" footer="0.511811023622047"/>
